--- a/scripts/data/template/data.xlsx
+++ b/scripts/data/template/data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="13">
   <si>
     <t>subject</t>
   </si>
@@ -2501,39 +2501,57 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5"/>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5"/>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="5"/>
+      <c r="K1" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="L1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="5"/>
+      <c r="M1" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="N1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="5"/>
+      <c r="O1" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="P1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="5"/>
+      <c r="Q1" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="R1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="5"/>
+      <c r="S1" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="1" spans="1:19">
       <c r="A2" t="s">
@@ -2595,17 +2613,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
